--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK BULL L.E MATURE BULL.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK BULL L.E MATURE BULL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$146</definedName>
@@ -4863,7 +4863,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -4932,7 +4936,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -5001,7 +5009,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -5070,7 +5082,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
           <t>50.0</t>
@@ -5139,7 +5155,11 @@
           <t>73.9</t>
         </is>
       </c>
-      <c r="N67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
           <t>13.3</t>
@@ -5208,7 +5228,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="N68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
           <t>11.0</t>
@@ -5277,7 +5301,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -5346,7 +5374,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -5415,7 +5447,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
           <t>12.3</t>
@@ -5484,7 +5520,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
           <t>10.5</t>
@@ -5553,7 +5593,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
           <t>11.5</t>
@@ -5622,7 +5666,11 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="N74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
           <t>19.8</t>
@@ -5691,7 +5739,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
           <t>14.0</t>
@@ -5760,7 +5812,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
           <t>8.3</t>
@@ -5829,7 +5885,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
           <t>14.9</t>
@@ -7416,7 +7476,11 @@
           <t>80.0</t>
         </is>
       </c>
-      <c r="N100" s="3" t="inlineStr"/>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
           <t>14.0</t>
@@ -7485,7 +7549,11 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="N101" s="5" t="inlineStr"/>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O101" s="5" t="inlineStr">
         <is>
           <t>13.0</t>
